--- a/shucle_report/해안면/20260330_20260405/report_해안면_20260330_20260405.xlsx
+++ b/shucle_report/해안면/20260330_20260405/report_해안면_20260330_20260405.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.03.30 ~ 04.05 | 비교기간: 2026.03.23 ~ 03.29 | 생성: 2026-04-08 15:27 | 차트: 81개</t>
+          <t>분석기간: 2026.03.30 ~ 04.05 | 비교기간: 2026.03.23 ~ 03.29 | 생성: 2026-04-13 12:37 | 차트: 174개</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8.8건</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7.8건</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10.4명</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -1509,21 +1509,21 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>• 대기시간 현황: 평균 3.5분</t>
+          <t>• 호출당 평균 탑승객 1.3명: 동승 이용 활발</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>• 가호출 성공률 안정: 92.0% → 96.7% (+5.1%)</t>
+          <t>• 수요 현황: 일평균 호출 8.8건, 이동완료 7.8건, 탑승객 10.4명</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>• 공급 현황: 운행차량 1.0대, 대당 운행시간 7.0시간</t>
+          <t>• 대기시간 현황: 평균 3.5분</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>비교기간 데이터 없음</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>비교기간 데이터 없음</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>비교기간 데이터 없음</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>비교기간 데이터 없음</t>
         </is>
       </c>
     </row>
